--- a/pipeline_output/TN_KL_2W_H&M.xlsx
+++ b/pipeline_output/TN_KL_2W_H&M.xlsx
@@ -736,12 +736,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1550,7 +1550,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1605,12 +1605,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2038,7 +2038,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2780,7 +2780,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3226,12 +3226,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3714,12 +3714,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3841,12 +3841,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4095,12 +4095,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5452,12 +5452,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5514,7 +5514,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5768,7 +5768,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -5833,12 +5833,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -5950,12 +5950,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6301,12 +6301,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6418,12 +6418,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6535,12 +6535,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6652,12 +6652,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -7588,12 +7588,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -7705,12 +7705,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7767,7 +7767,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -7884,7 +7884,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -7939,12 +7939,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8001,7 +8001,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -8056,12 +8056,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8469,7 +8469,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -8524,12 +8524,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8586,7 +8586,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -8758,12 +8758,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9054,7 +9054,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -9226,12 +9226,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -9460,12 +9460,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9522,7 +9522,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -9577,12 +9577,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9639,7 +9639,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -9694,12 +9694,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -10289,12 +10289,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -10543,12 +10543,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN85" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="AM86" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -11138,12 +11138,12 @@
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -11255,12 +11255,12 @@
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>750</t>
         </is>
       </c>
     </row>
@@ -11382,12 +11382,12 @@
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -11509,12 +11509,12 @@
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -11636,12 +11636,12 @@
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN92" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN93" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO93" t="inlineStr">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="AM94" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN94" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -12007,12 +12007,12 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN95" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO95" t="inlineStr">
@@ -12134,12 +12134,12 @@
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
@@ -12251,12 +12251,12 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
@@ -12378,12 +12378,12 @@
       </c>
       <c r="AM98" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
@@ -12505,12 +12505,12 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN99" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
@@ -12622,12 +12622,12 @@
       </c>
       <c r="AM100" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN100" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
@@ -12749,12 +12749,12 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN101" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN102" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -12938,7 +12938,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -12993,12 +12993,12 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
@@ -13055,7 +13055,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -13120,12 +13120,12 @@
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
@@ -13182,7 +13182,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -13247,12 +13247,12 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN105" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO105" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -13374,12 +13374,12 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN106" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO106" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -13501,12 +13501,12 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
@@ -13563,7 +13563,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -13618,12 +13618,12 @@
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -13735,12 +13735,12 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
@@ -13797,7 +13797,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
@@ -13914,7 +13914,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -14086,12 +14086,12 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
@@ -14148,7 +14148,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -14213,12 +14213,12 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -14340,12 +14340,12 @@
       </c>
       <c r="AM114" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -14467,12 +14467,12 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
@@ -14529,7 +14529,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -14594,12 +14594,12 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -14711,12 +14711,12 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -14838,12 +14838,12 @@
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -14900,7 +14900,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -14965,12 +14965,12 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
@@ -15027,7 +15027,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -15082,12 +15082,12 @@
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -15144,7 +15144,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
@@ -15209,12 +15209,12 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN121" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO121" t="inlineStr">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
@@ -15336,12 +15336,12 @@
       </c>
       <c r="AM122" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN122" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO122" t="inlineStr">
@@ -15398,7 +15398,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
@@ -15453,12 +15453,12 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN123" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO123" t="inlineStr">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
@@ -15580,12 +15580,12 @@
       </c>
       <c r="AM124" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN124" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO124" t="inlineStr">
@@ -15642,7 +15642,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, TAMIL NADU</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
@@ -15707,12 +15707,12 @@
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN125" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -15824,12 +15824,12 @@
       </c>
       <c r="AM126" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
@@ -15886,7 +15886,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -15951,12 +15951,12 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
@@ -16013,7 +16013,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
@@ -16078,12 +16078,12 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN128" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO128" t="inlineStr">
@@ -16140,7 +16140,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -16205,12 +16205,12 @@
       </c>
       <c r="AM129" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
@@ -16267,7 +16267,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -16332,12 +16332,12 @@
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -16449,12 +16449,12 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
@@ -16511,7 +16511,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -16566,12 +16566,12 @@
       </c>
       <c r="AM132" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -16628,7 +16628,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
@@ -16683,12 +16683,12 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN133" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO133" t="inlineStr">
@@ -16745,7 +16745,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="AM134" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -16862,7 +16862,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN135" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO135" t="inlineStr">
@@ -16979,7 +16979,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -17044,12 +17044,12 @@
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
@@ -17106,7 +17106,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
@@ -17171,12 +17171,12 @@
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
@@ -17233,7 +17233,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
@@ -17298,12 +17298,12 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN138" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
@@ -17360,7 +17360,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -17425,12 +17425,12 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
@@ -17487,7 +17487,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -17542,12 +17542,12 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN140" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
@@ -17604,7 +17604,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
@@ -17669,12 +17669,12 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -17796,12 +17796,12 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
@@ -17858,7 +17858,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -17913,12 +17913,12 @@
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -18040,12 +18040,12 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
@@ -18102,7 +18102,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -18167,12 +18167,12 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
@@ -18229,7 +18229,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -18284,12 +18284,12 @@
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
@@ -18346,7 +18346,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -18411,12 +18411,12 @@
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
@@ -18473,7 +18473,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>KERALA</t>
+          <t>KERALA, PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
@@ -18538,12 +18538,12 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
@@ -18665,12 +18665,12 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
@@ -18792,12 +18792,12 @@
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -18919,12 +18919,12 @@
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
@@ -19046,12 +19046,12 @@
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
@@ -19173,12 +19173,12 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN153" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO153" t="inlineStr">
@@ -19300,12 +19300,12 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN154" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO154" t="inlineStr">
@@ -19427,12 +19427,12 @@
       </c>
       <c r="AM155" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN155" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO155" t="inlineStr">
@@ -19554,12 +19554,12 @@
       </c>
       <c r="AM156" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN156" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -19671,12 +19671,12 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN157" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -19788,12 +19788,12 @@
       </c>
       <c r="AM158" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN158" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -19905,12 +19905,12 @@
       </c>
       <c r="AM159" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN159" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO159" t="inlineStr">
@@ -20022,12 +20022,12 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN160" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO160" t="inlineStr">
@@ -20139,12 +20139,12 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN161" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO161" t="inlineStr">
@@ -20256,12 +20256,12 @@
       </c>
       <c r="AM162" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -20373,12 +20373,12 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
@@ -20490,12 +20490,12 @@
       </c>
       <c r="AM164" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN164" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
@@ -20607,12 +20607,12 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN165" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
@@ -20724,12 +20724,12 @@
       </c>
       <c r="AM166" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN166" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
@@ -20841,12 +20841,12 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN167" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO167" t="inlineStr">
@@ -20958,12 +20958,12 @@
       </c>
       <c r="AM168" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN168" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -21075,12 +21075,12 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN169" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO169" t="inlineStr">
@@ -21192,12 +21192,12 @@
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN170" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO170" t="inlineStr">
@@ -21309,12 +21309,12 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN171" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO171" t="inlineStr">
@@ -21426,12 +21426,12 @@
       </c>
       <c r="AM172" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN172" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
@@ -21553,12 +21553,12 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
@@ -21680,12 +21680,12 @@
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
@@ -21807,12 +21807,12 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
@@ -21934,12 +21934,12 @@
       </c>
       <c r="AM176" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN176" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO176" t="inlineStr">
@@ -22061,12 +22061,12 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN177" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO177" t="inlineStr">
@@ -22188,12 +22188,12 @@
       </c>
       <c r="AM178" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN178" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO178" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN179" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO179" t="inlineStr">
@@ -22442,12 +22442,12 @@
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
@@ -22559,12 +22559,12 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
@@ -22676,12 +22676,12 @@
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -22793,12 +22793,12 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
@@ -22910,12 +22910,12 @@
       </c>
       <c r="AM184" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -23027,12 +23027,12 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
@@ -23144,12 +23144,12 @@
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -23261,12 +23261,12 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
@@ -23378,12 +23378,12 @@
       </c>
       <c r="AM188" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
@@ -23495,12 +23495,12 @@
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
@@ -23612,12 +23612,12 @@
       </c>
       <c r="AM190" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
@@ -23729,12 +23729,12 @@
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
@@ -23846,12 +23846,12 @@
       </c>
       <c r="AM192" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
@@ -23963,12 +23963,12 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN193" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
@@ -24080,12 +24080,12 @@
       </c>
       <c r="AM194" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
@@ -24197,12 +24197,12 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN195" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO195" t="inlineStr">
@@ -24314,12 +24314,12 @@
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN196" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
@@ -24376,7 +24376,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -24441,12 +24441,12 @@
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
@@ -24503,7 +24503,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -24568,12 +24568,12 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
@@ -24630,7 +24630,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -24695,12 +24695,12 @@
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
@@ -24757,7 +24757,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -24822,12 +24822,12 @@
       </c>
       <c r="AM200" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -24949,12 +24949,12 @@
       </c>
       <c r="AM201" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
@@ -25011,7 +25011,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -25076,12 +25076,12 @@
       </c>
       <c r="AM202" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
@@ -25138,7 +25138,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -25203,12 +25203,12 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN203" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
@@ -25265,7 +25265,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -25330,12 +25330,12 @@
       </c>
       <c r="AM204" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN204" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
@@ -25392,7 +25392,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
@@ -25447,12 +25447,12 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN205" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO205" t="inlineStr">
@@ -25509,7 +25509,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
@@ -25564,12 +25564,12 @@
       </c>
       <c r="AM206" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN206" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
@@ -25626,7 +25626,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -25681,12 +25681,12 @@
       </c>
       <c r="AM207" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN207" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
@@ -25743,7 +25743,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="AM208" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN208" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
@@ -25860,7 +25860,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
@@ -25915,12 +25915,12 @@
       </c>
       <c r="AM209" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN209" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO209" t="inlineStr">
@@ -25977,7 +25977,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -26032,12 +26032,12 @@
       </c>
       <c r="AM210" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN210" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO210" t="inlineStr">
@@ -26094,7 +26094,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -26149,12 +26149,12 @@
       </c>
       <c r="AM211" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN211" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -26211,7 +26211,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -26266,12 +26266,12 @@
       </c>
       <c r="AM212" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN212" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO212" t="inlineStr">
@@ -26328,7 +26328,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
@@ -26383,12 +26383,12 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN213" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
@@ -26445,7 +26445,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
@@ -26500,12 +26500,12 @@
       </c>
       <c r="AM214" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN214" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO214" t="inlineStr">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
@@ -26617,12 +26617,12 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN215" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO215" t="inlineStr">
@@ -26679,7 +26679,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -26734,12 +26734,12 @@
       </c>
       <c r="AM216" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN216" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO216" t="inlineStr">
@@ -26796,7 +26796,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -26851,12 +26851,12 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN217" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO217" t="inlineStr">
@@ -26913,7 +26913,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
@@ -26968,12 +26968,12 @@
       </c>
       <c r="AM218" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN218" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO218" t="inlineStr">
@@ -27030,7 +27030,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
@@ -27085,12 +27085,12 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN219" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO219" t="inlineStr">
@@ -27147,7 +27147,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>PUDUCHERRY</t>
+          <t>PUDUCHERRY, TAMIL NADU</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
@@ -27202,12 +27202,12 @@
       </c>
       <c r="AM220" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN220" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO220" t="inlineStr">
